--- a/checklist_forms/044_first_aid_kit_checklist_form--checklist_forms.xlsx
+++ b/checklist_forms/044_first_aid_kit_checklist_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_1</t>
+          <t>first_aid_kit_contents</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emergency Kit Contents</t>
+          <t>What are the contents of the first aid kit?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_2</t>
+          <t>first_aid_kit_item_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bandages</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Are the following items available in the first aid kit?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,58 +570,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_3</t>
+          <t>pain_relief_medication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wound Cleaning</t>
+          <t>Is there pain relief medication in the first aid kit?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_4</t>
+          <t>first_aid_kit_availability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bleeding Control</t>
+          <t>Do you have a first aid kit?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_5</t>
+          <t>medical_supplies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pain Relief</t>
+          <t>Are the following items in the first aid kit? (Select all that apply)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_6</t>
+          <t>first_aid_kit_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blister</t>
+          <t>Is the first aid kit located in an easy-to-access area?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +662,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_7</t>
+          <t>essential_items_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Antihistamines</t>
+          <t>Are all essential medical items in the first aid kit?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_8</t>
+          <t>first_aid_kit_stock_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Is the first aid kit well-stocked?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +703,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_9</t>
+          <t>first_aid_kit_location_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Gloves</t>
+          <t>What is the location of the first aid kit?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_10</t>
+          <t>medical_supplies_stock</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Aid Kit Contents</t>
+          <t>Are all medical supplies in the first aid kit?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +749,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_11</t>
+          <t>pain_relief_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medical Tape</t>
+          <t>Is pain relief medication available?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +772,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_12</t>
+          <t>first_aid_kit_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scissors</t>
+          <t>First Aid Kit Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_13</t>
+          <t>medical_gloves_status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thermometer</t>
+          <t>Are medical gloves available?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,18 +823,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_14</t>
+          <t>first_aid_kit_location_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>First Aid Kit Location</t>
+          <t>First Aid Kit Location 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_15</t>
+          <t>first_aid_kit_item_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>First Aid Kit Contents</t>
+          <t>First Aid Kit Item Status 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_16</t>
+          <t>first_aid_kit_contents_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>First Aid Kit Location</t>
+          <t>Are the following contents in the first aid kit? (Select all that apply)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +887,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_17</t>
+          <t>first_aid_kit_contents_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medical Gloves</t>
+          <t>First Aid Kit Contents 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_18</t>
+          <t>first_aid_kit_item_status_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>First Aid Kit Contents</t>
+          <t>First Aid Kit Item Status 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +933,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_19</t>
+          <t>first_aid_kit_stock_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Antihistamines</t>
+          <t>First Aid Kit Stock Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_20</t>
+          <t>medical_supplies_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Tape</t>
+          <t>Are the following supplies available?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +979,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_21</t>
+          <t>first_aid_kit_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scissors</t>
+          <t>Is the first aid kit available?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_22</t>
+          <t>first_aid_kit_contents_status_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thermometer</t>
+          <t>First Aid Kit Contents Status 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1025,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_23</t>
+          <t>first_aid_kit_location_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>First Aid Kit Location 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,46 +1048,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_24</t>
+          <t>medical_gloves</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>First Aid Kit Location</t>
+          <t>Medical Gloves</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_25</t>
+          <t>first_aid_kit_stock</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Medical Supplies</t>
+          <t>First Aid Kit Stock</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,517 +1130,517 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_2_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bandages</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bandages</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_2_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>wound_cleaning_supplies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Wound Cleaning Supplies</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_3_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>antiseptic_ointment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Antiseptic Ointment</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_3_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>antihistamines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Antihistamines</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_4_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medical_tape</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medical Tape</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_4_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scissors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_7_choices</t>
+          <t>first_aid_kit_item_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>thermometer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Thermometer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_7_choices</t>
+          <t>pain_relief_medication_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_8_choices</t>
+          <t>pain_relief_medication_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_8_choices</t>
+          <t>first_aid_kit_availability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_9_choices</t>
+          <t>first_aid_kit_availability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_9_choices</t>
+          <t>medical_supplies_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>antihistamines</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Antihistamines</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_10_choices</t>
+          <t>medical_supplies_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medical_tape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medical Tape</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_10_choices</t>
+          <t>medical_supplies_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scissors</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_11_choices</t>
+          <t>medical_supplies_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>thermometer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Thermometer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_11_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_12_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_12_choices</t>
+          <t>essential_items_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>antihistamines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Antihistamines</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_13_choices</t>
+          <t>essential_items_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medical_tape</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medical Tape</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_13_choices</t>
+          <t>essential_items_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scissors</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_15_choices</t>
+          <t>essential_items_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>thermometer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Thermometer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_15_choices</t>
+          <t>first_aid_kit_stock_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_16_choices</t>
+          <t>first_aid_kit_stock_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_16_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>antihistamines</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Antihistamines</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_17_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medical_tape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medical Tape</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_17_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scissors</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_18_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>thermometer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Thermometer</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_18_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bandages</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bandages</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_19_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>wound_cleaning_supplies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Wound Cleaning Supplies</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_19_choices</t>
+          <t>medical_supplies_stock_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>antiseptic_ointment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Antiseptic Ointment</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_20_choices</t>
+          <t>pain_relief_status_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1657,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_20_choices</t>
+          <t>pain_relief_status_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1674,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_21_choices</t>
+          <t>first_aid_kit_status_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1691,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_21_choices</t>
+          <t>first_aid_kit_status_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1708,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_22_choices</t>
+          <t>medical_gloves_status_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1725,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_22_choices</t>
+          <t>medical_gloves_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,32 +1742,695 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_23_choices</t>
+          <t>first_aid_kit_item_status_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>antihistamines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Antihistamines</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>first_aid_kit_checklist_form_page_23_choices</t>
+          <t>first_aid_kit_item_status_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medical_tape</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
+        <is>
+          <t>Medical Tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Scissors</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>thermometer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thermometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bandages</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bandages</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wound_cleaning_supplies</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wound Cleaning Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>antiseptic_ointment</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Antiseptic Ointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>medical_gloves</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Medical Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>antihistamines</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Antihistamines</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>medical_tape</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Medical Tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Scissors</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>thermometer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Thermometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bandages</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bandages</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wound_cleaning_supplies</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wound Cleaning Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>antiseptic_ointment</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Antiseptic Ointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>antihistamines</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Antihistamines</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>medical_tape</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Medical Tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Scissors</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>thermometer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Thermometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>bandages</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bandages</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>wound_cleaning_supplies</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wound Cleaning Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>first_aid_kit_item_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>antiseptic_ointment</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Antiseptic Ointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>first_aid_kit_stock_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>first_aid_kit_stock_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>medical_supplies_2_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>antihistamines</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Antihistamines</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>medical_supplies_2_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>medical_tape</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Medical Tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>medical_supplies_2_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Scissors</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>medical_supplies_2_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>thermometer</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Thermometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>first_aid_kit_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>first_aid_kit_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>antihistamines</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Antihistamines</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>medical_tape</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Medical Tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Scissors</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>thermometer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Thermometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>bandages</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bandages</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>wound_cleaning_supplies</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wound Cleaning Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>first_aid_kit_contents_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>antiseptic_ointment</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Antiseptic Ointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>medical_gloves_choices</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>medical_gloves_choices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>first_aid_kit_stock_choices</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>first_aid_kit_stock_choices</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
